--- a/results/no_unpooling/plots/06_gap_table.xlsx
+++ b/results/no_unpooling/plots/06_gap_table.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Gap %</t>
+          <t>Optimal</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -573,8 +573,10 @@
       <c r="B4" t="n">
         <v>96.33</v>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>8/100</t>
+        </is>
       </c>
       <c r="D4" t="n">
         <v>109.94</v>
@@ -634,8 +636,10 @@
       <c r="B5" t="n">
         <v>143.03</v>
       </c>
-      <c r="C5" t="n">
-        <v>0</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7/100</t>
+        </is>
       </c>
       <c r="D5" t="n">
         <v>161.55</v>
@@ -695,8 +699,10 @@
       <c r="B6" t="n">
         <v>187.76</v>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0/100</t>
+        </is>
       </c>
       <c r="D6" t="n">
         <v>204.67</v>
@@ -756,8 +762,10 @@
       <c r="B7" t="n">
         <v>191.07</v>
       </c>
-      <c r="C7" t="n">
-        <v>0</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0/100</t>
+        </is>
       </c>
       <c r="D7" t="n">
         <v>205.63</v>
@@ -817,8 +825,10 @@
       <c r="B8" t="n">
         <v>280.48</v>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0/100</t>
+        </is>
       </c>
       <c r="D8" t="n">
         <v>296.93</v>
@@ -878,8 +888,10 @@
       <c r="B9" t="n">
         <v>374.74</v>
       </c>
-      <c r="C9" t="n">
-        <v>0</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0/100</t>
+        </is>
       </c>
       <c r="D9" t="n">
         <v>394.16</v>
@@ -939,8 +951,10 @@
       <c r="B10" t="n">
         <v>470.37</v>
       </c>
-      <c r="C10" t="n">
-        <v>0</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0/100</t>
+        </is>
       </c>
       <c r="D10" t="n">
         <v>491.14</v>
@@ -1000,8 +1014,10 @@
       <c r="B11" t="n">
         <v>939.48</v>
       </c>
-      <c r="C11" t="n">
-        <v>0</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0/100</t>
+        </is>
       </c>
       <c r="D11" t="n">
         <v>974.36</v>
@@ -1058,40 +1074,62 @@
           <t>200x10</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>1919.26</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0/100</t>
+        </is>
+      </c>
       <c r="D12" t="n">
         <v>1951.78</v>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>1.741014237905788</v>
+      </c>
       <c r="F12" t="n">
         <v>1925.66</v>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>0.3834534570887586</v>
+      </c>
       <c r="H12" t="n">
         <v>1961.38</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>2.243899165510101</v>
+      </c>
       <c r="J12" t="n">
         <v>2012.16</v>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>4.886161473592739</v>
+      </c>
       <c r="L12" t="n">
         <v>2061.573333333333</v>
       </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>7.465801894582587</v>
+      </c>
       <c r="N12" t="n">
         <v>2056.106666666667</v>
       </c>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>7.180994827343792</v>
+      </c>
       <c r="P12" t="n">
         <v>2062.323333333333</v>
       </c>
-      <c r="Q12" t="inlineStr"/>
+      <c r="Q12" t="n">
+        <v>7.504915277358259</v>
+      </c>
       <c r="R12" t="n">
         <v>2062.85</v>
       </c>
-      <c r="S12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>7.531900859637008</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1099,24 +1137,34 @@
           <t>Mk</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="n">
+        <v>172.6</v>
+      </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
         <v>186.1</v>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>14.10752537233183</v>
+      </c>
       <c r="F13" t="n">
         <v>268</v>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>70.12821496062877</v>
+      </c>
       <c r="H13" t="n">
         <v>189.1</v>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>16.34450182048575</v>
+      </c>
       <c r="J13" t="n">
         <v>222.6</v>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>34.96766082550475</v>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1132,40 +1180,58 @@
           <t>edata</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="n">
+        <v>1697.030303030303</v>
+      </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
         <v>2045.121212121212</v>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>17.04347759731398</v>
+      </c>
       <c r="F14" t="n">
         <v>2045.257575757576</v>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>23.06149594518934</v>
+      </c>
       <c r="H14" t="n">
         <v>2093.863636363636</v>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>19.55408016987395</v>
+      </c>
       <c r="J14" t="n">
         <v>2243.712121212121</v>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>32.4150004948589</v>
+      </c>
       <c r="L14" t="n">
         <v>2038.075757575757</v>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>18.52673632945141</v>
+      </c>
       <c r="N14" t="n">
         <v>1884.010101010101</v>
       </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>10.66756312302494</v>
+      </c>
       <c r="P14" t="n">
         <v>2062.974747474747</v>
       </c>
-      <c r="Q14" t="inlineStr"/>
+      <c r="Q14" t="n">
+        <v>19.08147552263887</v>
+      </c>
       <c r="R14" t="n">
         <v>1879.555555555556</v>
       </c>
-      <c r="S14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>10.82228907097539</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1173,40 +1239,58 @@
           <t>rdata</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>1426.378787878788</v>
+      </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
         <v>1687.439393939394</v>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>14.46267902354886</v>
+      </c>
       <c r="F15" t="n">
         <v>1808.015151515152</v>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>26.46372593116812</v>
+      </c>
       <c r="H15" t="n">
         <v>1702.651515151515</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>16.3433911190802</v>
+      </c>
       <c r="J15" t="n">
         <v>1820.106060606061</v>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>27.72702408777951</v>
+      </c>
       <c r="L15" t="n">
         <v>1651.29797979798</v>
       </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>14.70937482828002</v>
+      </c>
       <c r="N15" t="n">
         <v>1535.722222222222</v>
       </c>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>8.274541568178652</v>
+      </c>
       <c r="P15" t="n">
         <v>1660.318181818182</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
+      <c r="Q15" t="n">
+        <v>15.12313498278646</v>
+      </c>
       <c r="R15" t="n">
         <v>1542.181818181818</v>
       </c>
-      <c r="S15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>8.672393499023507</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1214,40 +1298,58 @@
           <t>vdata</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="n">
+        <v>1365.939393939394</v>
+      </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
         <v>1442.560606060606</v>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>2.976799113029442</v>
+      </c>
       <c r="F16" t="n">
         <v>1617.121212121212</v>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>15.23668765513237</v>
+      </c>
       <c r="H16" t="n">
         <v>1514.530303030303</v>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>5.698985457182911</v>
+      </c>
       <c r="J16" t="n">
         <v>1639.787878787879</v>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>15.60004565321777</v>
+      </c>
       <c r="L16" t="n">
         <v>1446.934343434343</v>
       </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>4.716015796942246</v>
+      </c>
       <c r="N16" t="n">
         <v>1396.217171717172</v>
       </c>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>1.800800518062656</v>
+      </c>
       <c r="P16" t="n">
         <v>1454.484848484848</v>
       </c>
-      <c r="Q16" t="inlineStr"/>
+      <c r="Q16" t="n">
+        <v>5.195130908138435</v>
+      </c>
       <c r="R16" t="n">
         <v>1401.040404040404</v>
       </c>
-      <c r="S16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>1.910237086443663</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/results/no_unpooling/plots/06_gap_table.xlsx
+++ b/results/no_unpooling/plots/06_gap_table.xlsx
@@ -1138,32 +1138,36 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>172.6</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
+        <v>173.6</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
       <c r="D13" t="n">
         <v>186.1</v>
       </c>
       <c r="E13" t="n">
-        <v>14.10752537233183</v>
+        <v>13.50754612890539</v>
       </c>
       <c r="F13" t="n">
         <v>268</v>
       </c>
       <c r="G13" t="n">
-        <v>70.12821496062877</v>
+        <v>69.15552087134421</v>
       </c>
       <c r="H13" t="n">
         <v>189.1</v>
       </c>
       <c r="I13" t="n">
-        <v>16.34450182048575</v>
+        <v>15.72864681198988</v>
       </c>
       <c r="J13" t="n">
         <v>222.6</v>
       </c>
       <c r="K13" t="n">
-        <v>34.96766082550475</v>
+        <v>34.21560430137382</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
@@ -1181,56 +1185,60 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1697.030303030303</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
+        <v>1696.969696969697</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>59/66</t>
+        </is>
+      </c>
       <c r="D14" t="n">
         <v>2045.121212121212</v>
       </c>
       <c r="E14" t="n">
-        <v>17.04347759731398</v>
+        <v>17.05912655834206</v>
       </c>
       <c r="F14" t="n">
         <v>2045.257575757576</v>
       </c>
       <c r="G14" t="n">
-        <v>23.06149594518934</v>
+        <v>23.08042101648029</v>
       </c>
       <c r="H14" t="n">
         <v>2093.863636363636</v>
       </c>
       <c r="I14" t="n">
-        <v>19.55408016987395</v>
+        <v>19.56883810334718</v>
       </c>
       <c r="J14" t="n">
         <v>2243.712121212121</v>
       </c>
       <c r="K14" t="n">
-        <v>32.4150004948589</v>
+        <v>32.43358151878979</v>
       </c>
       <c r="L14" t="n">
         <v>2038.075757575757</v>
       </c>
       <c r="M14" t="n">
-        <v>18.52673632945141</v>
+        <v>18.54220570473099</v>
       </c>
       <c r="N14" t="n">
         <v>1884.010101010101</v>
       </c>
       <c r="O14" t="n">
-        <v>10.66756312302494</v>
+        <v>10.68217369100824</v>
       </c>
       <c r="P14" t="n">
         <v>2062.974747474747</v>
       </c>
       <c r="Q14" t="n">
-        <v>19.08147552263887</v>
+        <v>19.09700865539942</v>
       </c>
       <c r="R14" t="n">
         <v>1879.555555555556</v>
       </c>
       <c r="S14" t="n">
-        <v>10.82228907097539</v>
+        <v>10.83671848868576</v>
       </c>
     </row>
     <row r="15">
@@ -1240,56 +1248,60 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1426.378787878788</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
+        <v>1426.909090909091</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>34/66</t>
+        </is>
+      </c>
       <c r="D15" t="n">
         <v>1687.439393939394</v>
       </c>
       <c r="E15" t="n">
-        <v>14.46267902354886</v>
+        <v>14.4416374269675</v>
       </c>
       <c r="F15" t="n">
         <v>1808.015151515152</v>
       </c>
       <c r="G15" t="n">
-        <v>26.46372593116812</v>
+        <v>26.45123122328132</v>
       </c>
       <c r="H15" t="n">
         <v>1702.651515151515</v>
       </c>
       <c r="I15" t="n">
-        <v>16.3433911190802</v>
+        <v>16.32245045142188</v>
       </c>
       <c r="J15" t="n">
         <v>1820.106060606061</v>
       </c>
       <c r="K15" t="n">
-        <v>27.72702408777951</v>
+        <v>27.70990812434014</v>
       </c>
       <c r="L15" t="n">
         <v>1651.29797979798</v>
       </c>
       <c r="M15" t="n">
-        <v>14.70937482828002</v>
+        <v>14.68976945053365</v>
       </c>
       <c r="N15" t="n">
         <v>1535.722222222222</v>
       </c>
       <c r="O15" t="n">
-        <v>8.274541568178652</v>
+        <v>8.255445733813019</v>
       </c>
       <c r="P15" t="n">
         <v>1660.318181818182</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.12313498278646</v>
+        <v>15.10514757166034</v>
       </c>
       <c r="R15" t="n">
         <v>1542.181818181818</v>
       </c>
       <c r="S15" t="n">
-        <v>8.672393499023507</v>
+        <v>8.653736749196787</v>
       </c>
     </row>
     <row r="16">
@@ -1299,56 +1311,60 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1365.939393939394</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
+        <v>1366.984848484848</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>27/66</t>
+        </is>
+      </c>
       <c r="D16" t="n">
         <v>1442.560606060606</v>
       </c>
       <c r="E16" t="n">
-        <v>2.976799113029442</v>
+        <v>2.796517177892701</v>
       </c>
       <c r="F16" t="n">
         <v>1617.121212121212</v>
       </c>
       <c r="G16" t="n">
-        <v>15.23668765513237</v>
+        <v>15.025528413241</v>
       </c>
       <c r="H16" t="n">
         <v>1514.530303030303</v>
       </c>
       <c r="I16" t="n">
-        <v>5.698985457182911</v>
+        <v>5.51328268184553</v>
       </c>
       <c r="J16" t="n">
         <v>1639.787878787879</v>
       </c>
       <c r="K16" t="n">
-        <v>15.60004565321777</v>
+        <v>15.36170167065717</v>
       </c>
       <c r="L16" t="n">
         <v>1446.934343434343</v>
       </c>
       <c r="M16" t="n">
-        <v>4.716015796942246</v>
+        <v>4.532275893431197</v>
       </c>
       <c r="N16" t="n">
         <v>1396.217171717172</v>
       </c>
       <c r="O16" t="n">
-        <v>1.800800518062656</v>
+        <v>1.61913769567796</v>
       </c>
       <c r="P16" t="n">
         <v>1454.484848484848</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.195130908138435</v>
+        <v>5.012860841474232</v>
       </c>
       <c r="R16" t="n">
         <v>1401.040404040404</v>
       </c>
       <c r="S16" t="n">
-        <v>1.910237086443663</v>
+        <v>1.729088174895753</v>
       </c>
     </row>
   </sheetData>

--- a/results/no_unpooling/plots/06_gap_table.xlsx
+++ b/results/no_unpooling/plots/06_gap_table.xlsx
@@ -445,22 +445,22 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>SAGC (Greedy)</t>
+          <t>Song+SAGC (Greedy)</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>SAGC (Sampling)</t>
+          <t>Song+SAGC (Sampling)</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>NoPooling (Greedy)</t>
+          <t>Song (Greedy)</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>NoPooling (Sampling)</t>
+          <t>Song (Sampling)</t>
         </is>
       </c>
     </row>
